--- a/qa-reports/04-test-cases.xlsx
+++ b/qa-reports/04-test-cases.xlsx
@@ -7,8 +7,8 @@
     <sheet name="Summary" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Test Cases'!A1:Q73</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1">'Summary'!A1:B60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Test Cases'!$A$1:$Q$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1">Summary!$A$1:$B$60</definedName>
   </definedNames>
 </workbook>
 </file>
